--- a/data/gravel/Standert Kieswerk 2025.xlsx
+++ b/data/gravel/Standert Kieswerk 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B6680F-2CD3-FA4D-AE49-4C1BA706E4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F17393E-9C72-CA4D-BA1B-5D17E9693F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26120" yWindow="-26500" windowWidth="28220" windowHeight="23740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7640" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>aluminum</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0830/1771/files/shadow_front.webp?v=1720469280</t>
   </si>
 </sst>
 </file>
@@ -738,6 +741,11 @@
         <v>75</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Standert Kieswerk 2025.xlsx
+++ b/data/gravel/Standert Kieswerk 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F17393E-9C72-CA4D-BA1B-5D17E9693F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA537E75-B6FD-1B46-A723-80DB9D220909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7640" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8940" yWindow="920" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0830/1771/files/shadow_front.webp?v=1720469280</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Berlin, Germany</t>
   </si>
 </sst>
 </file>
@@ -695,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1666,6 +1672,14 @@
         <v>78</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Standert Kieswerk 2025.xlsx
+++ b/data/gravel/Standert Kieswerk 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA537E75-B6FD-1B46-A723-80DB9D220909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410438F6-E8C8-7545-80C2-86B119501908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="920" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>Berlin, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -701,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1515,168 +1533,198 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71">
-        <v>2449</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>103</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/gravel/Standert Kieswerk 2025.xlsx
+++ b/data/gravel/Standert Kieswerk 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410438F6-E8C8-7545-80C2-86B119501908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1F4D73-9176-4F42-BD39-41ABCA616260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -276,15 +276,6 @@
   </si>
   <si>
     <t>Measurement</t>
-  </si>
-  <si>
-    <t>48 PC™</t>
-  </si>
-  <si>
-    <t>50 PC™</t>
-  </si>
-  <si>
-    <t>52 PC™</t>
   </si>
   <si>
     <t>Seat Tube Length</t>
@@ -767,7 +758,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -775,7 +766,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="21">
@@ -785,14 +776,14 @@
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>83</v>
+      <c r="C8" s="1">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2">
+        <v>52</v>
       </c>
       <c r="F8" s="2">
         <v>54</v>
@@ -812,7 +803,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3">
         <v>460</v>
@@ -841,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3">
         <v>512</v>
@@ -870,7 +861,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="3">
         <v>100</v>
@@ -899,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C12" s="3">
         <v>75.5</v>
@@ -928,7 +919,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" s="3">
         <v>70.5</v>
@@ -957,7 +948,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3">
         <v>526</v>
@@ -986,7 +977,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" s="3">
         <v>376</v>
@@ -1015,7 +1006,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>430</v>
@@ -1044,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C17">
         <v>1012</v>
@@ -1073,7 +1064,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>750</v>
@@ -1102,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C19">
         <v>165</v>
@@ -1131,7 +1122,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C20">
         <f>K20*10</f>
@@ -1188,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <v>90</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -1464,7 +1455,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1533,32 +1524,32 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1619,7 +1610,7 @@
         <v>51</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1722,10 +1713,10 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
